--- a/artfynd/Lappberget artfynd.xlsx
+++ b/artfynd/Lappberget artfynd.xlsx
@@ -2497,7 +2497,7 @@
         <v>122743269</v>
       </c>
       <c r="B20" t="n">
-        <v>91863</v>
+        <v>91924</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>122743270</v>
       </c>
       <c r="B21" t="n">
-        <v>79361</v>
+        <v>79405</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>122743268</v>
       </c>
       <c r="B114" t="n">
-        <v>83311</v>
+        <v>83358</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
